--- a/outputs/Shear_metrics_reproducibility.xlsx
+++ b/outputs/Shear_metrics_reproducibility.xlsx
@@ -434,10 +434,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
@@ -1808,6 +1808,108 @@
       </c>
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>1988_Davies</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>1988</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Davies</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>A review of information relating to fish passage through turbines: Implications to tidal power schemes. Journa</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>turbine-passage injury mechanisms (incl. shear)</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>1997_Cada</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Cada</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Shaken, not stirred: the recipe for a fish-friendly turbine</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>biological design criteria (shear)</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2023_Koukouvinis</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Koukouvinis</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>State of the Art in Designing Fish-Friendly Turbines - Concepts and Performance Indicators</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>fish-friendly turbine design / CFD (shear)</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
